--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_ΠΑΡΙΣΗ_ΑΙΚΑΤΕΡΙΝΗ_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_ΠΑΡΙΣΗ_ΑΙΚΑΤΕΡΙΝΗ_2026-02.xlsx
@@ -2844,7 +2844,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3196,13 +3196,13 @@
         <v>2113.96</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0</v>
+        <v>63.757512</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>2.11</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>0</v>
+        <v>30.16</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3236,13 +3236,13 @@
         <v>1824</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0</v>
+        <v>31.9040908</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>1.82</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>0</v>
+        <v>17.49</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3416,13 +3416,13 @@
         <v>1843.46</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>15.243913</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>1.84</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>0</v>
+        <v>8.27</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3436,13 +3436,13 @@
         <v>1718.36</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>27.0592476</v>
+        <v>23.5723882</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>1.72</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>15.75</v>
+        <v>13.72</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3456,13 +3456,13 @@
         <v>2822.26</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0</v>
+        <v>54.3279828</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>2.82</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3476,13 +3476,13 @@
         <v>1201.38</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>2.3739782</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>1.2</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3496,13 +3496,13 @@
         <v>45294.96</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>1827.54</v>
+        <v>1991.66</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>45.29</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>40.35</v>
+        <v>43.97</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>1827.54</v>
+        <v>1991.66</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
